--- a/uploads/Prueba_nueva_Negociado.xlsx
+++ b/uploads/Prueba_nueva_Negociado.xlsx
@@ -2687,11 +2687,7 @@
           <t>REGULACIÓN</t>
         </is>
       </c>
-      <c r="M35" s="83" t="inlineStr">
-        <is>
-          <t>1.472,87</t>
-        </is>
-      </c>
+      <c r="M35" s="83" t="inlineStr"/>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="80" t="inlineStr">
